--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484194_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484194_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.5211</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2511</v>
+        <v>2.3531</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6357</v>
+        <v>-1.832</v>
       </c>
       <c r="G2" t="n">
         <v>2.465</v>
@@ -610,13 +610,13 @@
         <v>0.9919</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4484</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0171</v>
+        <v>0.1191</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4655</v>
+        <v>-0.6619</v>
       </c>
       <c r="V2" t="n">
         <v>-1.4012</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. LATORRE CIRIA</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3607</v>
+        <v>-0.0447</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6212</v>
+        <v>1.2347</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2605</v>
+        <v>-1.2795</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.1383</v>
+        <v>0.0956</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2848</v>
+        <v>0.1914</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1466</v>
+        <v>-0.0959</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6882</v>
+        <v>1.2153</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.8405</v>
+        <v>0.6505</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5287</v>
+        <v>0.5648</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8265</v>
+        <v>-1.1197</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4444</v>
+        <v>-0.459</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3821</v>
+        <v>-0.6607</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7216</v>
+        <v>-1.4695</v>
       </c>
       <c r="T3" t="n">
-        <v>1.933</v>
+        <v>-0.5838</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.2114</v>
+        <v>-0.8857</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.8097</v>
+        <v>0.3373</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.8097</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>R. GER SIERRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2309</v>
+        <v>-0.7429</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1327</v>
+        <v>0.1785</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3636</v>
+        <v>-0.9214</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0956</v>
+        <v>-0.1283</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1914</v>
+        <v>-0.5545</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0959</v>
+        <v>0.4262</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2153</v>
+        <v>0.3882</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6505</v>
+        <v>-0.2971</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5648</v>
+        <v>0.6853</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1197</v>
+        <v>-0.5165</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.459</v>
+        <v>-0.2574</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6607</v>
+        <v>-0.2591</v>
       </c>
       <c r="P4" t="n">
         <v>0.9919</v>
@@ -766,19 +766,19 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6557</v>
+        <v>-1.3405</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6858</v>
+        <v>-0.2097</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9699</v>
+        <v>-1.1308</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6032</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-0.266</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GER SIERRA</t>
+          <t>U. LATORRE CIRIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5949</v>
+        <v>-0.8356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3826</v>
+        <v>1.3969</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9775</v>
+        <v>-2.2325</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1283</v>
+        <v>-0.1383</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5545</v>
+        <v>-1.2848</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4262</v>
+        <v>1.1466</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3882</v>
+        <v>0.6882</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2971</v>
+        <v>-0.8405</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6853</v>
+        <v>1.5287</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5165</v>
+        <v>-0.8265</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2574</v>
+        <v>-0.4444</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2591</v>
+        <v>-0.3821</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1925</v>
+        <v>-0.4747</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0056</v>
+        <v>0.7086</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1869</v>
+        <v>-1.1833</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.266</v>
+        <v>-1.8097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5099</v>
+        <v>-0.9746</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.241</v>
+        <v>-0.4964</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2688</v>
+        <v>-0.4782</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5542</v>
+        <v>1.2252</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9221</v>
+        <v>0.4831</v>
       </c>
       <c r="I6" t="n">
-        <v>0.368</v>
+        <v>0.7422</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5985</v>
+        <v>2.1108</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1878</v>
+        <v>0.4489</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4108</v>
+        <v>1.6619</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1527</v>
+        <v>-0.8856000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1099</v>
+        <v>0.0342</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0428</v>
+        <v>-0.9198</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1984</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1822</v>
+        <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4913</v>
+        <v>-2.4019</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8557</v>
+        <v>-0.6234</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-1.7785</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3373</v>
+        <v>-0.1947</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3373</v>
+        <v>-0.1947</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.8393</v>
+        <v>-1.5022</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1086</v>
+        <v>-1.037</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7307</v>
+        <v>-0.4652</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2252</v>
+        <v>-0.5542</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4831</v>
+        <v>-0.9221</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7422</v>
+        <v>0.368</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1108</v>
+        <v>1.5985</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4489</v>
+        <v>0.1878</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6619</v>
+        <v>1.4108</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-2.1527</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0342</v>
+        <v>-1.1099</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9198</v>
+        <v>-1.0428</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.9838</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3806</v>
+        <v>2.1822</v>
       </c>
       <c r="S7" t="n">
-        <v>-3.2665</v>
+        <v>-1.4836</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2356</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-2.031</v>
+        <v>-0.832</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1947</v>
+        <v>0.3373</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1947</v>
+        <v>0.3373</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>I. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0191</v>
+        <v>-1.7466</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2599</v>
+        <v>-2.737</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7592</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9473</v>
+        <v>-1.7919</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1817</v>
+        <v>-1.4667</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.3252</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4938</v>
+        <v>-0.4983</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3332</v>
+        <v>-1.2288</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1606</v>
+        <v>0.7306</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4411</v>
+        <v>-1.2937</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5148</v>
+        <v>-0.2379</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9263</v>
+        <v>-1.0558</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7855</v>
+        <v>2.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4642</v>
+        <v>-1.2243</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2382</v>
+        <v>-0.2549</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7024</v>
+        <v>-0.9694</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4012</v>
+        <v>0.6745</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4012</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5519</v>
+        <v>-2.3377</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7788</v>
+        <v>0.8808</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3307</v>
+        <v>-3.2185</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3312</v>
@@ -1156,13 +1156,13 @@
         <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4272</v>
+        <v>-1.213</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.357</v>
+        <v>-0.2549</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0702</v>
+        <v>-0.958</v>
       </c>
       <c r="V9" t="n">
         <v>1.8097</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. TERREROS RIVAS</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8893</v>
+        <v>-2.996</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6553</v>
+        <v>-0.8721</v>
       </c>
       <c r="F10" t="n">
-        <v>0.766</v>
+        <v>-2.1239</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7919</v>
+        <v>-0.9473</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4667</v>
+        <v>-0.1817</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3252</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.4983</v>
+        <v>0.4938</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2288</v>
+        <v>0.3332</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7306</v>
+        <v>0.1606</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2937</v>
+        <v>-1.4411</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2379</v>
+        <v>-0.5148</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0558</v>
+        <v>-0.9263</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5952</v>
+        <v>0.7935</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>2.579</v>
+        <v>1.7855</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.367</v>
+        <v>-1.4411</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1732</v>
+        <v>-0.374</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1938</v>
+        <v>-1.0671</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6745</v>
+        <v>-1.4012</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6745</v>
+        <v>-1.4012</v>
       </c>
     </row>
     <row r="11">
@@ -1270,22 +1270,22 @@
         <v>-10.6592</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9015999999999997</v>
+        <v>0.9015000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.5607</v>
+        <v>-11.5608</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1054</v>
+        <v>-3.105399999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-8.4169</v>
+        <v>-8.416899999999998</v>
       </c>
       <c r="I11" t="n">
-        <v>5.311700000000001</v>
+        <v>5.3117</v>
       </c>
       <c r="J11" t="n">
-        <v>8.937099999999999</v>
+        <v>8.937100000000001</v>
       </c>
       <c r="K11" t="n">
         <v>-2.9161</v>
@@ -1300,7 +1300,7 @@
         <v>-5.5006</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.542</v>
+        <v>-6.542000000000001</v>
       </c>
       <c r="P11" t="n">
         <v>5.9516</v>
@@ -1312,16 +1312,16 @@
         <v>14.8788</v>
       </c>
       <c r="S11" t="n">
-        <v>-11.5912</v>
+        <v>-11.5914</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.1246</v>
+        <v>-2.1247</v>
       </c>
       <c r="U11" t="n">
         <v>-9.466699999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.914</v>
+        <v>-1.914000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>3.0161</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.9219</v>
+        <v>7.4966</v>
       </c>
       <c r="E12" t="n">
-        <v>6.1564</v>
+        <v>6.2585</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7655</v>
+        <v>1.2382</v>
       </c>
       <c r="G12" t="n">
         <v>3.9946</v>
@@ -1390,13 +1390,13 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1257</v>
+        <v>1.7005</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1337</v>
+        <v>1.2357</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.008</v>
+        <v>0.4647</v>
       </c>
       <c r="V12" t="n">
         <v>1.2065</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.088</v>
+        <v>4.1799</v>
       </c>
       <c r="E13" t="n">
-        <v>5.911</v>
+        <v>4.8907</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.823</v>
+        <v>-0.7108</v>
       </c>
       <c r="G13" t="n">
         <v>1.0972</v>
@@ -1468,13 +1468,13 @@
         <v>0.5952</v>
       </c>
       <c r="S13" t="n">
-        <v>3.181</v>
+        <v>2.2729</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8909</v>
+        <v>1.8706</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2901</v>
+        <v>0.4024</v>
       </c>
       <c r="V13" t="n">
         <v>1.2065</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5216</v>
+        <v>2.325</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.5799</v>
+        <v>2.8439</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1014</v>
+        <v>-0.5189</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0433</v>
+        <v>0.851</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3001</v>
+        <v>1.3757</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.3434</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1767</v>
+        <v>2.407</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7364000000000001</v>
+        <v>1.0792</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5597</v>
+        <v>1.3279</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.22</v>
+        <v>-1.556</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5637</v>
+        <v>0.2965</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7837</v>
+        <v>-1.8525</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R14" t="n">
         <v>0.9919</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8941</v>
+        <v>0.8502</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5645</v>
+        <v>0.805</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3296</v>
+        <v>0.0452</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3373</v>
+        <v>2.6076</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3373</v>
+        <v>2.6076</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.914</v>
+        <v>0.7595</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2377</v>
+        <v>-0.4421</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6763</v>
+        <v>1.2016</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9755</v>
+        <v>1.0698</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.0869</v>
+        <v>1.1787</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.8887</v>
+        <v>-0.1089</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.2178</v>
+        <v>1.621</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3785</v>
+        <v>0.4085</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1606</v>
+        <v>1.2125</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7577</v>
+        <v>-0.5512</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2916</v>
+        <v>0.7702</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0493</v>
+        <v>-1.3214</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5871</v>
+        <v>1.1903</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4964</v>
+        <v>0.4832</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6496</v>
+        <v>-0.0793</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1531</v>
+        <v>0.5625</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7979000000000001</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8082</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8236</v>
+        <v>-0.2724</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0154</v>
+        <v>0.9483</v>
       </c>
       <c r="G16" t="n">
-        <v>0.851</v>
+        <v>-1.9755</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3757</v>
+        <v>-1.0869</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.8887</v>
       </c>
       <c r="J16" t="n">
-        <v>2.407</v>
+        <v>-1.2178</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0792</v>
+        <v>-1.3785</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3279</v>
+        <v>0.1606</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.556</v>
+        <v>-0.7577</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2965</v>
+        <v>0.2916</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8525</v>
+        <v>-1.0493</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6666</v>
+        <v>1.2584</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2153</v>
+        <v>1.1394</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4513</v>
+        <v>0.1189</v>
       </c>
       <c r="V16" t="n">
-        <v>2.6076</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6076</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0511</v>
+        <v>0.5161</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1125</v>
+        <v>0.2593</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0614</v>
+        <v>0.2568</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1076</v>
+        <v>0.7141</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6048</v>
+        <v>0.4032</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7125</v>
+        <v>0.3108</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7812</v>
+        <v>1.0701</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5804</v>
+        <v>-0.0244</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2008</v>
+        <v>1.0946</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8888</v>
+        <v>-0.3561</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0244</v>
+        <v>0.4277</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9133</v>
+        <v>-0.7837</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.579</v>
+        <v>0.1984</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7377</v>
+        <v>1.2186</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3071</v>
+        <v>0.5896</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4307</v>
+        <v>0.6291</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.615</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2015</v>
+        <v>0.2599</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.659</v>
+        <v>-1.192</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4574</v>
+        <v>1.4519</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7141</v>
+        <v>-0.0433</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4032</v>
+        <v>1.3001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3108</v>
+        <v>-1.3434</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0701</v>
+        <v>0.1767</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0244</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0946</v>
+        <v>-0.5597</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3561</v>
+        <v>-0.22</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4277</v>
+        <v>0.5637</v>
       </c>
       <c r="O18" t="n">
         <v>-0.7837</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.501</v>
+        <v>1.6324</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3287</v>
+        <v>0.9523</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8297</v>
+        <v>0.68</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.615</v>
+        <v>-0.3373</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.4085</v>
+        <v>-0.3373</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3636</v>
+        <v>-0.6299</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9522</v>
+        <v>0.4599</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5886</v>
+        <v>-1.0898</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0698</v>
+        <v>-0.7065</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1787</v>
+        <v>-0.358</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1089</v>
+        <v>-0.3485</v>
       </c>
       <c r="J19" t="n">
-        <v>1.621</v>
+        <v>0.0805</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4085</v>
+        <v>0.0403</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2125</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5512</v>
+        <v>-0.787</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7702</v>
+        <v>-0.3983</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3214</v>
+        <v>-0.3886</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7935</v>
+        <v>0.3968</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6399</v>
+        <v>0.017</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5894</v>
+        <v>0.1134</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0505</v>
+        <v>-0.0964</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4259</v>
+        <v>-0.889</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6639</v>
+        <v>0.3326</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0898</v>
+        <v>-1.2216</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7065</v>
+        <v>-0.8592</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.358</v>
+        <v>1.5168</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3485</v>
+        <v>-2.376</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0805</v>
+        <v>0.6556</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0403</v>
+        <v>1.9758</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0402</v>
+        <v>-1.3202</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.787</v>
+        <v>-1.5148</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3983</v>
+        <v>-0.459</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3886</v>
+        <v>-1.0558</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3968</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
         <v>0.3968</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2211</v>
+        <v>0.5654</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3175</v>
+        <v>0.6689000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0964</v>
+        <v>-0.1035</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3373</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3711</v>
+        <v>-1.1392</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1776</v>
+        <v>-1.2139</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1935</v>
+        <v>0.0746</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8592</v>
+        <v>-0.1076</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5168</v>
+        <v>0.6048</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.376</v>
+        <v>-0.7125</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6556</v>
+        <v>0.7812</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9758</v>
+        <v>0.5804</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3202</v>
+        <v>0.2008</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5148</v>
+        <v>-0.8888</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.459</v>
+        <v>0.0244</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0558</v>
+        <v>-0.9133</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5952</v>
+        <v>-2.579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R21" t="n">
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0833</v>
+        <v>1.5474</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1587</v>
+        <v>0.9807</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.5667</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2834</v>
+        <v>-1.5352</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9758</v>
+        <v>-0.3637</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3076</v>
+        <v>-1.1716</v>
       </c>
       <c r="G22" t="n">
         <v>-0.9292</v>
@@ -2170,13 +2170,13 @@
         <v>0.5952</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6575</v>
+        <v>1.4057</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5782</v>
+        <v>1.1904</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0793</v>
+        <v>0.2153</v>
       </c>
       <c r="V22" t="n">
         <v>-1.615</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>10.6593</v>
+        <v>12.0196</v>
       </c>
       <c r="E23" t="n">
-        <v>11.5606</v>
+        <v>11.5608</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9015000000000002</v>
+        <v>0.4586999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>3.105399999999999</v>
+        <v>3.105400000000001</v>
       </c>
       <c r="H23" t="n">
         <v>8.4169</v>
@@ -2224,7 +2224,7 @@
         <v>12.0426</v>
       </c>
       <c r="K23" t="n">
-        <v>5.500699999999999</v>
+        <v>5.5007</v>
       </c>
       <c r="L23" t="n">
         <v>6.542000000000001</v>
@@ -2248,19 +2248,19 @@
         <v>8.9275</v>
       </c>
       <c r="S23" t="n">
-        <v>11.5913</v>
+        <v>12.9517</v>
       </c>
       <c r="T23" t="n">
-        <v>9.466800000000001</v>
+        <v>9.466699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1247</v>
+        <v>3.4849</v>
       </c>
       <c r="V23" t="n">
         <v>1.9139</v>
       </c>
       <c r="W23" t="n">
-        <v>4.930199999999999</v>
+        <v>4.9302</v>
       </c>
       <c r="X23" t="n">
         <v>-3.0162</v>
